--- a/diseases/d208/2005-2009.xlsx
+++ b/diseases/d208/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>22</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.4193605818589949</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>51</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>1.103150164261222</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>13</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.2478039801894061</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>40</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.8652158151068413</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>26</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.4956079603788122</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>38</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.8219550243514991</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>30</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.5718553388986295</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>61</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.319454118037933</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>24</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.4574842711189036</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>47</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>1.016628582750538</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>21</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.4002987372290406</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.9733677919951964</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>14</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.2668658248193604</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>36</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.7786942335961571</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>30</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.5718553388986295</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>36</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.7786942335961571</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>18</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3431132033391777</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>59</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>1.276193327282591</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>30</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.5718553388986295</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>49</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>1.05988937350588</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>31</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.5909171835285838</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>58</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>1.25456293190492</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>18</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.3431132033391777</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>51</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.103150164261222</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>23</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.4367437035087514</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>47</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.00847678379159</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>15</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.2848328501144031</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>33</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.7080794439387756</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>30</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.5696657002288062</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>51</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>1.094304595178108</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>24</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.455732560183045</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>33</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.7080794439387756</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>21</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.3987659901601643</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>54</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.158675453717996</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>18</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.3417994201372838</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>62</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>1.330331076491033</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>19</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.3607882768115773</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>31</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.6651655382455165</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>24</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.455732560183045</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>63</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>1.351788029337663</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>21</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.3987659901601643</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>44</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.9441059252517008</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>22</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.4177548468344579</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>46</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.9870198309449599</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>28</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.5316879868802191</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>50</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.072847642331478</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>13</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.2468551367658161</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>27</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.5793377268589982</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>23</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.4348886590491821</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>43</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.9131431022656566</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>14</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.2647148359429804</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>31</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.6583124690752409</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>12</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.226898430808269</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>49</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>1.040558418860865</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>19</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.3592558487797592</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>33</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.7007842412736435</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>16</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.3025312410776919</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>61</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>1.29538905205128</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>23</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.4348886590491821</v>
       </c>
@@ -24129,9 +23952,6 @@
       <c r="O120" t="n">
         <v>39</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.8281995578688515</v>
       </c>
@@ -24525,9 +24345,6 @@
       <c r="O122" t="n">
         <v>15</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2836230385103362</v>
       </c>
@@ -24921,9 +24738,6 @@
       <c r="O124" t="n">
         <v>25</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.5308971524800329</v>
       </c>
@@ -25317,9 +25131,6 @@
       <c r="O126" t="n">
         <v>22</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.4159804564818264</v>
       </c>
@@ -25713,9 +25524,6 @@
       <c r="O128" t="n">
         <v>54</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>1.146737849356871</v>
       </c>
@@ -26109,9 +25917,6 @@
       <c r="O130" t="n">
         <v>18</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.3403476462124034</v>
       </c>
@@ -26505,9 +26310,6 @@
       <c r="O132" t="n">
         <v>38</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.8069636717696501</v>
       </c>
@@ -26901,9 +26703,6 @@
       <c r="O134" t="n">
         <v>13</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.2458066333756247</v>
       </c>
@@ -27297,9 +27096,6 @@
       <c r="O136" t="n">
         <v>51</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>1.083030191059267</v>
       </c>
@@ -27693,9 +27489,6 @@
       <c r="O138" t="n">
         <v>12</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.226898430808269</v>
       </c>
@@ -28089,9 +27882,6 @@
       <c r="O140" t="n">
         <v>54</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.146737849356871</v>
       </c>
@@ -28485,9 +28275,6 @@
       <c r="O142" t="n">
         <v>17</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.3214394436450477</v>
       </c>
@@ -28881,9 +28668,6 @@
       <c r="O144" t="n">
         <v>30</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.6370765829760395</v>
       </c>
@@ -29277,9 +29061,6 @@
       <c r="O146" t="n">
         <v>20</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.3764084498427271</v>
       </c>
@@ -29673,9 +29454,6 @@
       <c r="O148" t="n">
         <v>58</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.216417185793673</v>
       </c>
@@ -30069,9 +29847,6 @@
       <c r="O150" t="n">
         <v>29</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.5457922522719544</v>
       </c>
@@ -30465,9 +30240,6 @@
       <c r="O152" t="n">
         <v>72</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>1.510035127192146</v>
       </c>
@@ -30861,9 +30633,6 @@
       <c r="O154" t="n">
         <v>24</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.4516901398112726</v>
       </c>
@@ -31257,9 +31026,6 @@
       <c r="O156" t="n">
         <v>32</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.6711267231965095</v>
       </c>
@@ -31653,9 +31419,6 @@
       <c r="O158" t="n">
         <v>18</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.3387676048584544</v>
       </c>
@@ -32049,9 +31812,6 @@
       <c r="O160" t="n">
         <v>58</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>1.216417185793673</v>
       </c>
@@ -32445,9 +32205,6 @@
       <c r="O162" t="n">
         <v>27</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.5081514072876816</v>
       </c>
@@ -32841,9 +32598,6 @@
       <c r="O164" t="n">
         <v>60</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>1.258362605993455</v>
       </c>
@@ -33237,9 +32991,6 @@
       <c r="O166" t="n">
         <v>21</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.3952288723348635</v>
       </c>
@@ -33633,9 +33384,6 @@
       <c r="O168" t="n">
         <v>52</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.090580925194328</v>
       </c>
@@ -34029,9 +33777,6 @@
       <c r="O170" t="n">
         <v>25</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.4705105623034089</v>
       </c>
@@ -34425,9 +34170,6 @@
       <c r="O172" t="n">
         <v>46</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.9647446645949823</v>
       </c>
@@ -34821,9 +34563,6 @@
       <c r="O174" t="n">
         <v>18</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.3387676048584544</v>
       </c>
@@ -35217,9 +34956,6 @@
       <c r="O176" t="n">
         <v>61</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>1.279335316093346</v>
       </c>
@@ -35613,9 +35349,6 @@
       <c r="O178" t="n">
         <v>31</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.5834330972562271</v>
       </c>
@@ -36009,9 +35742,6 @@
       <c r="O180" t="n">
         <v>69</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>1.447116996892474</v>
       </c>
@@ -36405,9 +36135,6 @@
       <c r="O182" t="n">
         <v>34</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.6398943647326362</v>
       </c>
@@ -36801,9 +36528,6 @@
       <c r="O184" t="n">
         <v>66</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>1.384198866592801</v>
       </c>
@@ -37197,9 +36921,6 @@
       <c r="O186" t="n">
         <v>21</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.3952288723348635</v>
       </c>
@@ -37593,9 +37314,6 @@
       <c r="O188" t="n">
         <v>54</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>1.13252634539411</v>
       </c>
@@ -37989,9 +37707,6 @@
       <c r="O190" t="n">
         <v>21</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.3952288723348635</v>
       </c>
@@ -38385,9 +38100,6 @@
       <c r="O192" t="n">
         <v>55</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>1.153499055494001</v>
       </c>
@@ -38781,9 +38493,6 @@
       <c r="O194" t="n">
         <v>37</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.6930323000814875</v>
       </c>
@@ -39177,9 +38886,6 @@
       <c r="O196" t="n">
         <v>65</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>1.34613960813876</v>
       </c>
@@ -39573,9 +39279,6 @@
       <c r="O198" t="n">
         <v>26</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.4869956703275317</v>
       </c>
@@ -39969,9 +39672,6 @@
       <c r="O200" t="n">
         <v>71</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>1.47039864889003</v>
       </c>
@@ -40365,9 +40065,6 @@
       <c r="O202" t="n">
         <v>41</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.7679547109011077</v>
       </c>
@@ -40761,9 +40458,6 @@
       <c r="O204" t="n">
         <v>79</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>1.636077369891724</v>
       </c>
@@ -41157,9 +40851,6 @@
       <c r="O206" t="n">
         <v>27</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.5057262730324368</v>
       </c>
@@ -41553,9 +41244,6 @@
       <c r="O208" t="n">
         <v>58</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>1.201170727262278</v>
       </c>
@@ -41949,9 +41637,6 @@
       <c r="O210" t="n">
         <v>31</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.580648683852057</v>
       </c>
@@ -42345,9 +42030,6 @@
       <c r="O212" t="n">
         <v>75</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>1.553238009390877</v>
       </c>
@@ -42741,9 +42423,6 @@
       <c r="O214" t="n">
         <v>37</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.6930323000814875</v>
       </c>
@@ -43137,9 +42816,6 @@
       <c r="O216" t="n">
         <v>77</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>1.594657689641301</v>
       </c>
@@ -43533,9 +43209,6 @@
       <c r="O218" t="n">
         <v>24</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.4495344649177216</v>
       </c>
@@ -43929,9 +43602,6 @@
       <c r="O220" t="n">
         <v>62</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>1.284010087763125</v>
       </c>
@@ -44325,9 +43995,6 @@
       <c r="O222" t="n">
         <v>21</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.3933426568030064</v>
       </c>
@@ -44721,9 +44388,6 @@
       <c r="O224" t="n">
         <v>62</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>1.284010087763125</v>
       </c>
@@ -45117,9 +44781,6 @@
       <c r="O226" t="n">
         <v>25</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.4682650676226267</v>
       </c>
@@ -45513,9 +45174,6 @@
       <c r="O228" t="n">
         <v>71</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>1.47039864889003</v>
       </c>
@@ -45909,9 +45567,6 @@
       <c r="O230" t="n">
         <v>31</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.580648683852057</v>
       </c>
@@ -46305,9 +45960,6 @@
       <c r="O232" t="n">
         <v>74</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>1.532528169265665</v>
       </c>
@@ -46701,9 +46353,6 @@
       <c r="O234" t="n">
         <v>25</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.4682650676226267</v>
       </c>
@@ -47097,9 +46746,6 @@
       <c r="O236" t="n">
         <v>60</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>1.242590407512702</v>
       </c>
@@ -47493,9 +47139,6 @@
       <c r="O238" t="n">
         <v>20</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.3746120540981014</v>
       </c>
@@ -47888,9 +47531,6 @@
       </c>
       <c r="O240" t="n">
         <v>68</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>1.408269128514395</v>
